--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-ResultatsExamensBiologieMedicale.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-ResultatsExamensBiologieMedicale.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="121">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T14:36:02+00:00</t>
+    <t>2025-06-05T15:38:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -258,6 +258,138 @@
   </si>
   <si>
     <t>Code dont dérive le code de section</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.statut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Niveau de complétude</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.dateResultat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date et heure des résultats</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.choice[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/SujetNonHumain
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/PatientSujetNonHumain</t>
+  </si>
+  <si>
+    <t>Sujet non humain ou Patient avec sujet non humain</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.laboratoireExecutant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/LaboratoireExecutant
+</t>
+  </si>
+  <si>
+    <t>Laboratoire sous-traitant. Apparaît à ce niveau si et et seulement si ce résultat a été produit par un laboratoire exécutant distinct du laboratoire exécutant déclaré aux niveaux supérieurs.</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.auteur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Auteur
+</t>
+  </si>
+  <si>
+    <t>Participation d'un auteur au document. Apparaît à ce niveau si le compte-rendu de cette analyse procède de cet auteur spécifique.</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.valideur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ParticipantCorps
+</t>
+  </si>
+  <si>
+    <t>Valideur de ces résultats</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.responsable</t>
+  </si>
+  <si>
+    <t>Responsable de cet examen</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.dispositifAutomatique</t>
+  </si>
+  <si>
+    <t>Dispositif automatique impliqué dans la production des résultats</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.prelevement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Prelevement
+</t>
+  </si>
+  <si>
+    <t>Prélèvement</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.batterieExamensDeBiologieMedicale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/BatterieExamensDeBiologieMedicale
+</t>
+  </si>
+  <si>
+    <t>Batterie d'examens de biologie médicale</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.isolatMicrobiologique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/IsolatMicrobiologique
+</t>
+  </si>
+  <si>
+    <t>Isolat microbiologique</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.resultatElementCliniquePertinent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ResultatExamensBiologieElementCliniquePertinent
+</t>
+  </si>
+  <si>
+    <t>Résultat d'examen de biologie / élément clinique pertinent</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.imageIllustrative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ImageIllustrative
+</t>
+  </si>
+  <si>
+    <t>Image ou graphe</t>
+  </si>
+  <si>
+    <t>ResultatsExamensBiologieMedicale.commentaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/CommentaireER
+</t>
+  </si>
+  <si>
+    <t>Commentaire</t>
   </si>
 </sst>
 </file>
@@ -559,11 +691,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AJ17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.9765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.9765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.03515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="58.03515625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -572,7 +704,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="14.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="94.515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -593,7 +725,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="32.9765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="58.03515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -909,6 +1041,1406 @@
         <v>72</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L4" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M4" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="2"/>
+      <c r="R4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M5" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q5" s="2"/>
+      <c r="R5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AG5" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-ResultatsExamensBiologieMedicale.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-ResultatsExamensBiologieMedicale.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05T15:38:56+00:00</t>
+    <t>2025-10-06T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
